--- a/data/keywords_STANDARDIZED.xlsx
+++ b/data/keywords_STANDARDIZED.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sluca.POLIQUETA\Documents\review_ws\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sluca.POLIQUETA\Documents\RAUNK-SHORTFALLS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622ACDD8-C445-4F87-B842-9D8427621986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44F4984-D639-45A0-9D8D-3E0EDBC25572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="922">
   <si>
     <t>DI</t>
   </si>
@@ -2209,18 +2209,6 @@
     <t>MOUNEYRAC C;PELLERIN J;MOUKRIM A;AIT A A;DUROU C;VIAULT N</t>
   </si>
   <si>
-    <t>10.1016/j.marenvres.2018.09.013</t>
-  </si>
-  <si>
-    <t>RENZ J;POWILLEIT M;GOGINA M;ZETTLER M;MORYS C;FORSTER S</t>
-  </si>
-  <si>
-    <t>10.3989/scimar.2006.70s3301</t>
-  </si>
-  <si>
-    <t>GAMBI M;CIGLIANO M</t>
-  </si>
-  <si>
     <t>ANIMAL-SEDIMENT INTERACTIONS; MACROFAUNA; BIOTURBATION; BULK DENSITY; BURROWING BEHAVIOR; GRAIN SIZE; INTERTIDAL MUDFLAT</t>
   </si>
   <si>
@@ -2257,9 +2245,6 @@
     <t>BIOACCUMULATION; BIVALVES; DIETARY PATHWAY; KINETICS; MERCURY; POLYCHAETA</t>
   </si>
   <si>
-    <t>EUNICIDAE; LYSIDICE; MEDITERRANEAN SEA; NEMATONEREIS; POLYCHAETA; POSIDONIA OCEANICA; REPRODUCTIVE BIOLOGY</t>
-  </si>
-  <si>
     <t>BENTHIC ECOLOGY; POLYCHAETA; BIOTURBATION; SUBTIDAL SEDIMENTARY BOTTOM; TEMPORAL VARIATION; NE ATLANTIC</t>
   </si>
   <si>
@@ -2606,9 +2591,6 @@
   </si>
   <si>
     <t>BENTHIC INVERTEBRATES; BENTHIC MICROALGAE; BIODIVERSITY; ECOSYSTEM FUNCTIONING; EUTROPHICATION; GRAZING; MACROALGAE; NUTRIENT SUPPLY</t>
-  </si>
-  <si>
-    <t>BALTIC SEA; BENTHIC COMMUNITY; CLASSIFICATION; ECOSYSTEM FUNCTIONING; MACROFAUNA</t>
   </si>
   <si>
     <t>ECOSYSTEM FUNCTIONING; FUNCTIONAL TRAIT; ESTUARINE MACROFAUNA; SEDIMENT; SALINITY GRADIENT</t>
@@ -3144,7 +3126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C322"/>
+  <dimension ref="A1:C320"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="192.21875" bestFit="1" customWidth="1"/>
@@ -3167,7 +3149,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -3178,7 +3160,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -3189,7 +3171,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -3200,7 +3182,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -3211,7 +3193,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -3233,7 +3215,7 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -3244,7 +3226,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -3266,7 +3248,7 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -3277,7 +3259,7 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
@@ -3299,7 +3281,7 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -3310,7 +3292,7 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="C15" t="s">
         <v>33</v>
@@ -3321,7 +3303,7 @@
         <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="C16" t="s">
         <v>35</v>
@@ -3332,7 +3314,7 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C17" t="s">
         <v>37</v>
@@ -3343,7 +3325,7 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="C18" t="s">
         <v>39</v>
@@ -3354,7 +3336,7 @@
         <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="C19" t="s">
         <v>41</v>
@@ -3365,7 +3347,7 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="C20" t="s">
         <v>43</v>
@@ -3398,7 +3380,7 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="C23" t="s">
         <v>51</v>
@@ -3409,7 +3391,7 @@
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C24" t="s">
         <v>53</v>
@@ -3439,7 +3421,7 @@
         <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C27" t="s">
         <v>60</v>
@@ -3450,7 +3432,7 @@
         <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="C28" t="s">
         <v>62</v>
@@ -3502,7 +3484,7 @@
         <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="C33" t="s">
         <v>75</v>
@@ -3513,7 +3495,7 @@
         <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C34" t="s">
         <v>77</v>
@@ -3524,7 +3506,7 @@
         <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="C35" t="s">
         <v>79</v>
@@ -3535,7 +3517,7 @@
         <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C36" t="s">
         <v>81</v>
@@ -3557,7 +3539,7 @@
         <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C38" t="s">
         <v>86</v>
@@ -3568,7 +3550,7 @@
         <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="C39" t="s">
         <v>88</v>
@@ -3579,7 +3561,7 @@
         <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="C40" t="s">
         <v>90</v>
@@ -3590,7 +3572,7 @@
         <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="C41" t="s">
         <v>92</v>
@@ -3612,7 +3594,7 @@
         <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="C43" t="s">
         <v>97</v>
@@ -3623,7 +3605,7 @@
         <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -3634,7 +3616,7 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="C45" t="s">
         <v>101</v>
@@ -3645,7 +3627,7 @@
         <v>102</v>
       </c>
       <c r="B46" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -3656,7 +3638,7 @@
         <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C47" t="s">
         <v>105</v>
@@ -3667,7 +3649,7 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="C48" t="s">
         <v>107</v>
@@ -3678,7 +3660,7 @@
         <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="C49" t="s">
         <v>109</v>
@@ -3689,7 +3671,7 @@
         <v>110</v>
       </c>
       <c r="B50" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C50" t="s">
         <v>111</v>
@@ -3700,7 +3682,7 @@
         <v>112</v>
       </c>
       <c r="B51" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C51" t="s">
         <v>113</v>
@@ -3711,7 +3693,7 @@
         <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="C52" t="s">
         <v>115</v>
@@ -3722,7 +3704,7 @@
         <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="C53" t="s">
         <v>117</v>
@@ -3733,7 +3715,7 @@
         <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C54" t="s">
         <v>119</v>
@@ -3744,7 +3726,7 @@
         <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C55" t="s">
         <v>121</v>
@@ -3755,7 +3737,7 @@
         <v>122</v>
       </c>
       <c r="B56" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C56" t="s">
         <v>123</v>
@@ -3766,7 +3748,7 @@
         <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="C57" t="s">
         <v>125</v>
@@ -3777,7 +3759,7 @@
         <v>126</v>
       </c>
       <c r="B58" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="C58" t="s">
         <v>127</v>
@@ -3788,7 +3770,7 @@
         <v>128</v>
       </c>
       <c r="B59" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="C59" t="s">
         <v>129</v>
@@ -3799,7 +3781,7 @@
         <v>130</v>
       </c>
       <c r="B60" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C60" t="s">
         <v>131</v>
@@ -3810,7 +3792,7 @@
         <v>132</v>
       </c>
       <c r="B61" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C61" t="s">
         <v>133</v>
@@ -3821,7 +3803,7 @@
         <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="C62" t="s">
         <v>135</v>
@@ -3832,7 +3814,7 @@
         <v>136</v>
       </c>
       <c r="B63" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="C63" t="s">
         <v>137</v>
@@ -3854,7 +3836,7 @@
         <v>141</v>
       </c>
       <c r="B65" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C65" t="s">
         <v>142</v>
@@ -3865,7 +3847,7 @@
         <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C66" t="s">
         <v>144</v>
@@ -3876,7 +3858,7 @@
         <v>145</v>
       </c>
       <c r="B67" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="C67" t="s">
         <v>146</v>
@@ -3887,7 +3869,7 @@
         <v>147</v>
       </c>
       <c r="B68" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C68" t="s">
         <v>148</v>
@@ -3898,7 +3880,7 @@
         <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="C69" t="s">
         <v>150</v>
@@ -3909,7 +3891,7 @@
         <v>151</v>
       </c>
       <c r="B70" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="C70" t="s">
         <v>152</v>
@@ -3920,7 +3902,7 @@
         <v>153</v>
       </c>
       <c r="B71" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C71" t="s">
         <v>154</v>
@@ -3931,7 +3913,7 @@
         <v>155</v>
       </c>
       <c r="B72" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="C72" t="s">
         <v>156</v>
@@ -3942,7 +3924,7 @@
         <v>157</v>
       </c>
       <c r="B73" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C73" t="s">
         <v>158</v>
@@ -3953,7 +3935,7 @@
         <v>159</v>
       </c>
       <c r="B74" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C74" t="s">
         <v>160</v>
@@ -3975,7 +3957,7 @@
         <v>164</v>
       </c>
       <c r="B76" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="C76" t="s">
         <v>165</v>
@@ -4032,7 +4014,7 @@
         <v>178</v>
       </c>
       <c r="B82" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C82" t="s">
         <v>179</v>
@@ -4043,7 +4025,7 @@
         <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="C83" t="s">
         <v>181</v>
@@ -4054,7 +4036,7 @@
         <v>182</v>
       </c>
       <c r="B84" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="C84" t="s">
         <v>183</v>
@@ -4065,7 +4047,7 @@
         <v>184</v>
       </c>
       <c r="B85" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C85" t="s">
         <v>185</v>
@@ -4076,7 +4058,7 @@
         <v>186</v>
       </c>
       <c r="B86" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="C86" t="s">
         <v>187</v>
@@ -4098,7 +4080,7 @@
         <v>191</v>
       </c>
       <c r="B88" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="C88" t="s">
         <v>192</v>
@@ -4109,7 +4091,7 @@
         <v>193</v>
       </c>
       <c r="B89" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C89" t="s">
         <v>194</v>
@@ -4131,7 +4113,7 @@
         <v>198</v>
       </c>
       <c r="B91" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C91" t="s">
         <v>199</v>
@@ -4142,7 +4124,7 @@
         <v>200</v>
       </c>
       <c r="B92" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C92" t="s">
         <v>201</v>
@@ -4153,7 +4135,7 @@
         <v>202</v>
       </c>
       <c r="B93" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C93" t="s">
         <v>203</v>
@@ -4164,7 +4146,7 @@
         <v>204</v>
       </c>
       <c r="B94" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C94" t="s">
         <v>205</v>
@@ -4186,7 +4168,7 @@
         <v>209</v>
       </c>
       <c r="B96" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="C96" t="s">
         <v>210</v>
@@ -4197,7 +4179,7 @@
         <v>211</v>
       </c>
       <c r="B97" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="C97" t="s">
         <v>212</v>
@@ -4208,7 +4190,7 @@
         <v>213</v>
       </c>
       <c r="B98" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="C98" t="s">
         <v>214</v>
@@ -4230,7 +4212,7 @@
         <v>218</v>
       </c>
       <c r="B100" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="C100" t="s">
         <v>219</v>
@@ -4241,7 +4223,7 @@
         <v>220</v>
       </c>
       <c r="B101" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="C101" t="s">
         <v>221</v>
@@ -4263,7 +4245,7 @@
         <v>225</v>
       </c>
       <c r="B103" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="C103" t="s">
         <v>226</v>
@@ -4307,7 +4289,7 @@
         <v>236</v>
       </c>
       <c r="B107" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="C107" t="s">
         <v>237</v>
@@ -4318,7 +4300,7 @@
         <v>238</v>
       </c>
       <c r="B108" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C108" t="s">
         <v>239</v>
@@ -4340,7 +4322,7 @@
         <v>243</v>
       </c>
       <c r="B110" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="C110" t="s">
         <v>244</v>
@@ -4362,7 +4344,7 @@
         <v>248</v>
       </c>
       <c r="B112" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="C112" t="s">
         <v>249</v>
@@ -4384,7 +4366,7 @@
         <v>253</v>
       </c>
       <c r="B114" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C114" t="s">
         <v>254</v>
@@ -4395,7 +4377,7 @@
         <v>255</v>
       </c>
       <c r="B115" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="C115" t="s">
         <v>256</v>
@@ -4428,7 +4410,7 @@
         <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="C118" t="s">
         <v>264</v>
@@ -4439,7 +4421,7 @@
         <v>265</v>
       </c>
       <c r="B119" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="C119" t="s">
         <v>266</v>
@@ -4461,7 +4443,7 @@
         <v>270</v>
       </c>
       <c r="B121" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C121" t="s">
         <v>271</v>
@@ -4480,7 +4462,7 @@
         <v>274</v>
       </c>
       <c r="B123" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C123" t="s">
         <v>275</v>
@@ -4491,7 +4473,7 @@
         <v>276</v>
       </c>
       <c r="B124" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="C124" t="s">
         <v>277</v>
@@ -4513,7 +4495,7 @@
         <v>281</v>
       </c>
       <c r="B126" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="C126" t="s">
         <v>282</v>
@@ -4524,7 +4506,7 @@
         <v>283</v>
       </c>
       <c r="B127" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C127" t="s">
         <v>284</v>
@@ -4546,7 +4528,7 @@
         <v>288</v>
       </c>
       <c r="B129" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="C129" t="s">
         <v>289</v>
@@ -4557,7 +4539,7 @@
         <v>290</v>
       </c>
       <c r="B130" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="C130" t="s">
         <v>291</v>
@@ -4568,7 +4550,7 @@
         <v>292</v>
       </c>
       <c r="B131" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="C131" t="s">
         <v>293</v>
@@ -4579,7 +4561,7 @@
         <v>294</v>
       </c>
       <c r="B132" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C132" t="s">
         <v>295</v>
@@ -4590,7 +4572,7 @@
         <v>296</v>
       </c>
       <c r="B133" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="C133" t="s">
         <v>297</v>
@@ -4645,7 +4627,7 @@
         <v>310</v>
       </c>
       <c r="B138" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C138" t="s">
         <v>311</v>
@@ -4656,7 +4638,7 @@
         <v>312</v>
       </c>
       <c r="B139" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C139" t="s">
         <v>313</v>
@@ -4667,7 +4649,7 @@
         <v>314</v>
       </c>
       <c r="B140" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C140" t="s">
         <v>315</v>
@@ -4678,7 +4660,7 @@
         <v>316</v>
       </c>
       <c r="B141" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="C141" t="s">
         <v>317</v>
@@ -4689,7 +4671,7 @@
         <v>318</v>
       </c>
       <c r="B142" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="C142" t="s">
         <v>319</v>
@@ -4711,7 +4693,7 @@
         <v>323</v>
       </c>
       <c r="B144" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="C144" t="s">
         <v>324</v>
@@ -4733,7 +4715,7 @@
         <v>328</v>
       </c>
       <c r="B146" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C146" t="s">
         <v>329</v>
@@ -4766,7 +4748,7 @@
         <v>336</v>
       </c>
       <c r="B149" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C149" t="s">
         <v>337</v>
@@ -4788,7 +4770,7 @@
         <v>341</v>
       </c>
       <c r="B151" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C151" t="s">
         <v>342</v>
@@ -4799,7 +4781,7 @@
         <v>343</v>
       </c>
       <c r="B152" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="C152" t="s">
         <v>344</v>
@@ -4810,7 +4792,7 @@
         <v>345</v>
       </c>
       <c r="B153" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C153" t="s">
         <v>346</v>
@@ -4821,7 +4803,7 @@
         <v>347</v>
       </c>
       <c r="B154" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="C154" t="s">
         <v>348</v>
@@ -4843,7 +4825,7 @@
         <v>352</v>
       </c>
       <c r="B156" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C156" t="s">
         <v>353</v>
@@ -4854,7 +4836,7 @@
         <v>354</v>
       </c>
       <c r="B157" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="C157" t="s">
         <v>355</v>
@@ -4865,7 +4847,7 @@
         <v>356</v>
       </c>
       <c r="B158" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="C158" t="s">
         <v>357</v>
@@ -4876,7 +4858,7 @@
         <v>358</v>
       </c>
       <c r="B159" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C159" t="s">
         <v>359</v>
@@ -4898,7 +4880,7 @@
         <v>363</v>
       </c>
       <c r="B161" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C161" t="s">
         <v>364</v>
@@ -4909,7 +4891,7 @@
         <v>365</v>
       </c>
       <c r="B162" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="C162" t="s">
         <v>366</v>
@@ -4920,7 +4902,7 @@
         <v>367</v>
       </c>
       <c r="B163" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="C163" t="s">
         <v>368</v>
@@ -4931,7 +4913,7 @@
         <v>369</v>
       </c>
       <c r="B164" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C164" t="s">
         <v>370</v>
@@ -4942,7 +4924,7 @@
         <v>371</v>
       </c>
       <c r="B165" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C165" t="s">
         <v>372</v>
@@ -4953,7 +4935,7 @@
         <v>373</v>
       </c>
       <c r="B166" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="C166" t="s">
         <v>374</v>
@@ -4964,7 +4946,7 @@
         <v>375</v>
       </c>
       <c r="B167" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="C167" t="s">
         <v>376</v>
@@ -4975,7 +4957,7 @@
         <v>377</v>
       </c>
       <c r="B168" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="C168" t="s">
         <v>378</v>
@@ -4986,7 +4968,7 @@
         <v>379</v>
       </c>
       <c r="B169" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="C169" t="s">
         <v>380</v>
@@ -4997,7 +4979,7 @@
         <v>381</v>
       </c>
       <c r="B170" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C170" t="s">
         <v>382</v>
@@ -5019,7 +5001,7 @@
         <v>386</v>
       </c>
       <c r="B172" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C172" t="s">
         <v>387</v>
@@ -5038,7 +5020,7 @@
         <v>390</v>
       </c>
       <c r="B174" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="C174" t="s">
         <v>391</v>
@@ -5049,7 +5031,7 @@
         <v>392</v>
       </c>
       <c r="B175" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="C175" t="s">
         <v>393</v>
@@ -5068,7 +5050,7 @@
         <v>396</v>
       </c>
       <c r="B177" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="C177" t="s">
         <v>397</v>
@@ -5090,7 +5072,7 @@
         <v>401</v>
       </c>
       <c r="B179" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C179" t="s">
         <v>402</v>
@@ -5101,7 +5083,7 @@
         <v>403</v>
       </c>
       <c r="B180" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C180" t="s">
         <v>404</v>
@@ -5131,7 +5113,7 @@
         <v>410</v>
       </c>
       <c r="B183" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="C183" t="s">
         <v>411</v>
@@ -5142,7 +5124,7 @@
         <v>412</v>
       </c>
       <c r="B184" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C184" t="s">
         <v>413</v>
@@ -5175,7 +5157,7 @@
         <v>420</v>
       </c>
       <c r="B187" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C187" t="s">
         <v>421</v>
@@ -5186,7 +5168,7 @@
         <v>422</v>
       </c>
       <c r="B188" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C188" t="s">
         <v>423</v>
@@ -5208,7 +5190,7 @@
         <v>427</v>
       </c>
       <c r="B190" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C190" t="s">
         <v>428</v>
@@ -5230,7 +5212,7 @@
         <v>432</v>
       </c>
       <c r="B192" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C192" t="s">
         <v>433</v>
@@ -5241,7 +5223,7 @@
         <v>434</v>
       </c>
       <c r="B193" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="C193" t="s">
         <v>435</v>
@@ -5252,7 +5234,7 @@
         <v>436</v>
       </c>
       <c r="B194" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="C194" t="s">
         <v>437</v>
@@ -5263,7 +5245,7 @@
         <v>438</v>
       </c>
       <c r="B195" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="C195" t="s">
         <v>439</v>
@@ -5282,7 +5264,7 @@
         <v>442</v>
       </c>
       <c r="B197" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="C197" t="s">
         <v>443</v>
@@ -5293,7 +5275,7 @@
         <v>444</v>
       </c>
       <c r="B198" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C198" t="s">
         <v>445</v>
@@ -5326,7 +5308,7 @@
         <v>452</v>
       </c>
       <c r="B201" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="C201" t="s">
         <v>453</v>
@@ -5337,7 +5319,7 @@
         <v>454</v>
       </c>
       <c r="B202" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="C202" t="s">
         <v>455</v>
@@ -5348,7 +5330,7 @@
         <v>456</v>
       </c>
       <c r="B203" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C203" t="s">
         <v>457</v>
@@ -5370,7 +5352,7 @@
         <v>461</v>
       </c>
       <c r="B205" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="C205" t="s">
         <v>462</v>
@@ -5381,7 +5363,7 @@
         <v>463</v>
       </c>
       <c r="B206" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="C206" t="s">
         <v>464</v>
@@ -5392,7 +5374,7 @@
         <v>465</v>
       </c>
       <c r="B207" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C207" t="s">
         <v>466</v>
@@ -5411,7 +5393,7 @@
         <v>469</v>
       </c>
       <c r="B209" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="C209" t="s">
         <v>470</v>
@@ -5444,7 +5426,7 @@
         <v>477</v>
       </c>
       <c r="B212" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C212" t="s">
         <v>478</v>
@@ -5455,7 +5437,7 @@
         <v>479</v>
       </c>
       <c r="B213" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C213" t="s">
         <v>480</v>
@@ -5466,7 +5448,7 @@
         <v>481</v>
       </c>
       <c r="B214" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="C214" t="s">
         <v>482</v>
@@ -5477,7 +5459,7 @@
         <v>483</v>
       </c>
       <c r="B215" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="C215" t="s">
         <v>484</v>
@@ -5529,7 +5511,7 @@
         <v>496</v>
       </c>
       <c r="B220" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="C220" t="s">
         <v>497</v>
@@ -5540,7 +5522,7 @@
         <v>498</v>
       </c>
       <c r="B221" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C221" t="s">
         <v>499</v>
@@ -5567,7 +5549,7 @@
         <v>504</v>
       </c>
       <c r="B224" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C224" t="s">
         <v>505</v>
@@ -5594,7 +5576,7 @@
         <v>510</v>
       </c>
       <c r="B227" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="C227" t="s">
         <v>511</v>
@@ -5605,7 +5587,7 @@
         <v>512</v>
       </c>
       <c r="B228" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="C228" t="s">
         <v>513</v>
@@ -5668,7 +5650,7 @@
         <v>528</v>
       </c>
       <c r="B234" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="C234" t="s">
         <v>529</v>
@@ -5679,7 +5661,7 @@
         <v>530</v>
       </c>
       <c r="B235" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="C235" t="s">
         <v>531</v>
@@ -5720,7 +5702,7 @@
         <v>540</v>
       </c>
       <c r="B239" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C239" t="s">
         <v>541</v>
@@ -5731,7 +5713,7 @@
         <v>542</v>
       </c>
       <c r="B240" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="C240" t="s">
         <v>543</v>
@@ -5742,7 +5724,7 @@
         <v>544</v>
       </c>
       <c r="B241" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="C241" t="s">
         <v>545</v>
@@ -5764,7 +5746,7 @@
         <v>549</v>
       </c>
       <c r="B243" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="C243" t="s">
         <v>550</v>
@@ -5775,7 +5757,7 @@
         <v>551</v>
       </c>
       <c r="B244" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="C244" t="s">
         <v>552</v>
@@ -5786,7 +5768,7 @@
         <v>553</v>
       </c>
       <c r="B245" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="C245" t="s">
         <v>554</v>
@@ -5797,7 +5779,7 @@
         <v>555</v>
       </c>
       <c r="B246" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="C246" t="s">
         <v>556</v>
@@ -5838,7 +5820,7 @@
         <v>565</v>
       </c>
       <c r="B250" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="C250" t="s">
         <v>566</v>
@@ -5849,7 +5831,7 @@
         <v>567</v>
       </c>
       <c r="B251" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="C251" t="s">
         <v>568</v>
@@ -5868,7 +5850,7 @@
         <v>571</v>
       </c>
       <c r="B253" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C253" t="s">
         <v>572</v>
@@ -5890,7 +5872,7 @@
         <v>576</v>
       </c>
       <c r="B255" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="C255" t="s">
         <v>577</v>
@@ -5901,7 +5883,7 @@
         <v>578</v>
       </c>
       <c r="B256" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="C256" t="s">
         <v>579</v>
@@ -5920,7 +5902,7 @@
         <v>582</v>
       </c>
       <c r="B258" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="C258" t="s">
         <v>583</v>
@@ -5931,7 +5913,7 @@
         <v>584</v>
       </c>
       <c r="B259" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="C259" t="s">
         <v>585</v>
@@ -5953,7 +5935,7 @@
         <v>589</v>
       </c>
       <c r="B261" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C261" t="s">
         <v>590</v>
@@ -6010,7 +5992,7 @@
         <v>602</v>
       </c>
       <c r="B267" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="C267" t="s">
         <v>603</v>
@@ -6048,7 +6030,7 @@
         <v>611</v>
       </c>
       <c r="B271" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="C271" t="s">
         <v>612</v>
@@ -6059,7 +6041,7 @@
         <v>613</v>
       </c>
       <c r="B272" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C272" t="s">
         <v>614</v>
@@ -6070,7 +6052,7 @@
         <v>615</v>
       </c>
       <c r="B273" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C273" t="s">
         <v>616</v>
@@ -6092,7 +6074,7 @@
         <v>620</v>
       </c>
       <c r="B275" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C275" t="s">
         <v>621</v>
@@ -6114,7 +6096,7 @@
         <v>625</v>
       </c>
       <c r="B277" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C277" t="s">
         <v>626</v>
@@ -6125,7 +6107,7 @@
         <v>627</v>
       </c>
       <c r="B278" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="C278" t="s">
         <v>628</v>
@@ -6136,7 +6118,7 @@
         <v>629</v>
       </c>
       <c r="B279" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="C279" t="s">
         <v>630</v>
@@ -6174,7 +6156,7 @@
         <v>638</v>
       </c>
       <c r="B283" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="C283" t="s">
         <v>639</v>
@@ -6207,7 +6189,7 @@
         <v>646</v>
       </c>
       <c r="B286" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C286" t="s">
         <v>647</v>
@@ -6245,7 +6227,7 @@
         <v>655</v>
       </c>
       <c r="B290" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="C290" t="s">
         <v>656</v>
@@ -6264,7 +6246,7 @@
         <v>659</v>
       </c>
       <c r="B292" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="C292" t="s">
         <v>660</v>
@@ -6283,7 +6265,7 @@
         <v>663</v>
       </c>
       <c r="B294" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="C294" t="s">
         <v>664</v>
@@ -6294,7 +6276,7 @@
         <v>665</v>
       </c>
       <c r="B295" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="C295" t="s">
         <v>666</v>
@@ -6305,7 +6287,7 @@
         <v>667</v>
       </c>
       <c r="B296" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C296" t="s">
         <v>668</v>
@@ -6316,7 +6298,7 @@
         <v>669</v>
       </c>
       <c r="B297" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C297" t="s">
         <v>670</v>
@@ -6327,7 +6309,7 @@
         <v>671</v>
       </c>
       <c r="B298" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="C298" t="s">
         <v>672</v>
@@ -6338,7 +6320,7 @@
         <v>673</v>
       </c>
       <c r="B299" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="C299" t="s">
         <v>674</v>
@@ -6382,7 +6364,7 @@
         <v>684</v>
       </c>
       <c r="B303" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="C303" t="s">
         <v>685</v>
@@ -6453,7 +6435,7 @@
         <v>702</v>
       </c>
       <c r="B310" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C310" t="s">
         <v>703</v>
@@ -6486,7 +6468,7 @@
         <v>709</v>
       </c>
       <c r="B313" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="C313" t="s">
         <v>710</v>
@@ -6519,7 +6501,7 @@
         <v>717</v>
       </c>
       <c r="B316" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="C316" t="s">
         <v>718</v>
@@ -6561,28 +6543,6 @@
       </c>
       <c r="C320" t="s">
         <v>728</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A321" t="s">
-        <v>729</v>
-      </c>
-      <c r="B321" t="s">
-        <v>862</v>
-      </c>
-      <c r="C321" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A322" t="s">
-        <v>731</v>
-      </c>
-      <c r="B322" t="s">
-        <v>745</v>
-      </c>
-      <c r="C322" t="s">
-        <v>732</v>
       </c>
     </row>
   </sheetData>
